--- a/tests/projectWorkSpace/HCM/CoreHR/HireAnEmployeeTestData.xlsx
+++ b/tests/projectWorkSpace/HCM/CoreHR/HireAnEmployeeTestData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
   <si>
     <t>Dataset</t>
   </si>
@@ -109,6 +109,9 @@
     <t>SalaryAmount</t>
   </si>
   <si>
+    <t>Include_terminated_work_relationships</t>
+  </si>
+  <si>
     <t>Country</t>
   </si>
   <si>
@@ -182,6 +185,9 @@
   </si>
   <si>
     <t>Expat USD Equivalent Annual Salary Basis</t>
+  </si>
+  <si>
+    <t>False</t>
   </si>
 </sst>
 </file>
@@ -237,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -248,17 +254,14 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -580,41 +583,42 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="19.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="11" width="15.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="19.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="10" width="15.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -672,10 +676,10 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -708,58 +712,61 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P2" s="6">
         <v>212</v>
@@ -768,7 +775,7 @@
         <v>7123813</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S2" s="6">
         <v>123</v>
@@ -777,40 +784,43 @@
         <v>21225</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AE2" s="7">
         <v>4000</v>
       </c>
-      <c r="AF2" s="5" t="s">
-        <v>47</v>
+      <c r="AF2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG2" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -832,8 +842,8 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="1"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
@@ -844,8 +854,9 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="6"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1"/>
@@ -866,8 +877,8 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -878,8 +889,9 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="6"/>
+      <c r="AE4" s="4"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="5"/>
@@ -900,8 +912,8 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="1"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
@@ -912,8 +924,9 @@
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="6"/>
+      <c r="AE5" s="4"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1"/>
@@ -934,8 +947,8 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
@@ -946,8 +959,9 @@
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="6"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1"/>
@@ -968,8 +982,8 @@
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -980,8 +994,9 @@
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="6"/>
+      <c r="AE7" s="4"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1"/>
@@ -1002,8 +1017,8 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="1"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
@@ -1014,8 +1029,9 @@
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="6"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
